--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/122.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/122.xlsx
@@ -426,13 +426,13 @@
         <v>-18.62379274749276</v>
       </c>
       <c r="E2">
-        <v>-13.06051509206758</v>
+        <v>-14.9043647968227</v>
       </c>
       <c r="F2">
-        <v>-3.717848074898345</v>
+        <v>-4.369672160078415</v>
       </c>
       <c r="G2">
-        <v>-9.499810208339362</v>
+        <v>-10.02628295490412</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.65101595938163</v>
       </c>
       <c r="E3">
-        <v>-13.98191916993426</v>
+        <v>-16.04160953131698</v>
       </c>
       <c r="F3">
-        <v>-3.538990298755487</v>
+        <v>-4.319325646071066</v>
       </c>
       <c r="G3">
-        <v>-10.21258390512661</v>
+        <v>-10.39664030547346</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.66067787143725</v>
       </c>
       <c r="E4">
-        <v>-13.66291987541194</v>
+        <v>-15.18124475459969</v>
       </c>
       <c r="F4">
-        <v>-3.527348423276543</v>
+        <v>-3.724612523109606</v>
       </c>
       <c r="G4">
-        <v>-9.824756805746524</v>
+        <v>-10.38949614819972</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.61399305957581</v>
       </c>
       <c r="E5">
-        <v>-15.06701852623021</v>
+        <v>-16.65859600096603</v>
       </c>
       <c r="F5">
-        <v>-3.763750397789674</v>
+        <v>-3.85751910268437</v>
       </c>
       <c r="G5">
-        <v>-8.057091015052675</v>
+        <v>-10.10320016996355</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.50050245220585</v>
       </c>
       <c r="E6">
-        <v>-15.7046321949842</v>
+        <v>-17.5174709097348</v>
       </c>
       <c r="F6">
-        <v>-3.850151603003871</v>
+        <v>-3.974320563213906</v>
       </c>
       <c r="G6">
-        <v>-8.419721552333362</v>
+        <v>-9.869952373448655</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.29039993514448</v>
       </c>
       <c r="E7">
-        <v>-15.37567931459302</v>
+        <v>-17.72566297376344</v>
       </c>
       <c r="F7">
-        <v>-3.174777032562212</v>
+        <v>-3.970703911133283</v>
       </c>
       <c r="G7">
-        <v>-8.482757649946624</v>
+        <v>-10.74614784023648</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.97103921884508</v>
       </c>
       <c r="E8">
-        <v>-16.30705056375058</v>
+        <v>-17.95450940774106</v>
       </c>
       <c r="F8">
-        <v>-3.790303714886412</v>
+        <v>-3.855498714588942</v>
       </c>
       <c r="G8">
-        <v>-10.11271798838895</v>
+        <v>-9.935093978024895</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.52987139450993</v>
       </c>
       <c r="E9">
-        <v>-17.57974195581427</v>
+        <v>-18.92532819397944</v>
       </c>
       <c r="F9">
-        <v>-2.960455191170701</v>
+        <v>-3.496932428980551</v>
       </c>
       <c r="G9">
-        <v>-7.690802324951092</v>
+        <v>-9.25820328433781</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.95525692437519</v>
       </c>
       <c r="E10">
-        <v>-19.03149826708927</v>
+        <v>-18.52740212597743</v>
       </c>
       <c r="F10">
-        <v>-3.833744129856621</v>
+        <v>-3.430604222670992</v>
       </c>
       <c r="G10">
-        <v>-8.171371047068316</v>
+        <v>-9.896112304299976</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.25543367544394</v>
       </c>
       <c r="E11">
-        <v>-18.14381773515771</v>
+        <v>-19.82039919549151</v>
       </c>
       <c r="F11">
-        <v>-3.141637366245815</v>
+        <v>-3.381986511433286</v>
       </c>
       <c r="G11">
-        <v>-8.207753942544906</v>
+        <v>-10.34187064007176</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.43699233981934</v>
       </c>
       <c r="E12">
-        <v>-18.20860661278545</v>
+        <v>-19.42533059458835</v>
       </c>
       <c r="F12">
-        <v>-3.434380749660354</v>
+        <v>-3.398270557837519</v>
       </c>
       <c r="G12">
-        <v>-8.117349564958488</v>
+        <v>-9.444683004019417</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.51038740707908</v>
       </c>
       <c r="E13">
-        <v>-18.68179591879494</v>
+        <v>-21.10185318476005</v>
       </c>
       <c r="F13">
-        <v>-3.203397126328935</v>
+        <v>-3.181583727511015</v>
       </c>
       <c r="G13">
-        <v>-7.977786896659433</v>
+        <v>-9.478208898695616</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.5165059292368</v>
       </c>
       <c r="E14">
-        <v>-20.40633391886997</v>
+        <v>-21.30304422797283</v>
       </c>
       <c r="F14">
-        <v>-3.13535419949558</v>
+        <v>-3.367271392889955</v>
       </c>
       <c r="G14">
-        <v>-7.267823853035031</v>
+        <v>-7.885578271754113</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.4843450597761</v>
       </c>
       <c r="E15">
-        <v>-19.22211985196815</v>
+        <v>-21.88955406755026</v>
       </c>
       <c r="F15">
-        <v>-2.842650577716375</v>
+        <v>-3.37490976871117</v>
       </c>
       <c r="G15">
-        <v>-7.29453333444587</v>
+        <v>-7.624442439616401</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.46045427360446</v>
       </c>
       <c r="E16">
-        <v>-20.20322733115195</v>
+        <v>-22.35264034804864</v>
       </c>
       <c r="F16">
-        <v>-2.839019015022502</v>
+        <v>-3.123134123569482</v>
       </c>
       <c r="G16">
-        <v>-6.294496980124988</v>
+        <v>-7.250390520225229</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.49197789449067</v>
       </c>
       <c r="E17">
-        <v>-22.33076781859159</v>
+        <v>-24.1203528193128</v>
       </c>
       <c r="F17">
-        <v>-1.986525411616461</v>
+        <v>-3.10684427859343</v>
       </c>
       <c r="G17">
-        <v>-4.920633823509602</v>
+        <v>-6.98697041166542</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.616686923235104</v>
       </c>
       <c r="E18">
-        <v>-25.20415250356855</v>
+        <v>-24.20942337456967</v>
       </c>
       <c r="F18">
-        <v>-2.33656613991524</v>
+        <v>-2.88408965704142</v>
       </c>
       <c r="G18">
-        <v>-6.199673024243643</v>
+        <v>-6.900230807990976</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.880580159225495</v>
       </c>
       <c r="E19">
-        <v>-25.00075609351403</v>
+        <v>-24.38543157382579</v>
       </c>
       <c r="F19">
-        <v>-2.396514260488437</v>
+        <v>-3.014671837683929</v>
       </c>
       <c r="G19">
-        <v>-5.488991592237219</v>
+        <v>-6.538461012550499</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.306617262733029</v>
       </c>
       <c r="E20">
-        <v>-23.92496727977786</v>
+        <v>-25.00109572906461</v>
       </c>
       <c r="F20">
-        <v>-2.701462809215825</v>
+        <v>-2.628776054722377</v>
       </c>
       <c r="G20">
-        <v>-5.133482038411504</v>
+        <v>-6.638277271105065</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.904704873252878</v>
       </c>
       <c r="E21">
-        <v>-25.87759093019722</v>
+        <v>-26.4871507024737</v>
       </c>
       <c r="F21">
-        <v>-2.206144662548874</v>
+        <v>-2.476053270137843</v>
       </c>
       <c r="G21">
-        <v>-5.176207939141338</v>
+        <v>-6.212074327833752</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.685240351017065</v>
       </c>
       <c r="E22">
-        <v>-25.7523559815151</v>
+        <v>-26.60155806980348</v>
       </c>
       <c r="F22">
-        <v>-2.270107051556038</v>
+        <v>-2.186366562439633</v>
       </c>
       <c r="G22">
-        <v>-4.737501065368199</v>
+        <v>-5.992419631303109</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.632817950237706</v>
       </c>
       <c r="E23">
-        <v>-26.3327070964421</v>
+        <v>-27.15482891016462</v>
       </c>
       <c r="F23">
-        <v>-1.910859847942546</v>
+        <v>-2.096665141492683</v>
       </c>
       <c r="G23">
-        <v>-4.707341995505438</v>
+        <v>-6.945115184412415</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.731674564118264</v>
       </c>
       <c r="E24">
-        <v>-27.44596450411774</v>
+        <v>-28.12428009725268</v>
       </c>
       <c r="F24">
-        <v>-1.371994426910425</v>
+        <v>-2.046958955487699</v>
       </c>
       <c r="G24">
-        <v>-4.40208652296586</v>
+        <v>-5.649268343975494</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.950419496922954</v>
       </c>
       <c r="E25">
-        <v>-28.14598507317144</v>
+        <v>-27.76683405840523</v>
       </c>
       <c r="F25">
-        <v>-1.805452581038517</v>
+        <v>-1.856799762868447</v>
       </c>
       <c r="G25">
-        <v>-4.375122129548496</v>
+        <v>-6.647295197154039</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.25585814209462</v>
       </c>
       <c r="E26">
-        <v>-26.87691646031389</v>
+        <v>-28.09784739446991</v>
       </c>
       <c r="F26">
-        <v>-1.479510717221981</v>
+        <v>-1.779460897040877</v>
       </c>
       <c r="G26">
-        <v>-5.116048705601702</v>
+        <v>-5.584106876126019</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.620672271075392</v>
       </c>
       <c r="E27">
-        <v>-27.68601438279034</v>
+        <v>-28.83874196991684</v>
       </c>
       <c r="F27">
-        <v>-1.522253646839033</v>
+        <v>-1.999643437807194</v>
       </c>
       <c r="G27">
-        <v>-5.152756034541141</v>
+        <v>-5.355248862996202</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.01030856084264</v>
       </c>
       <c r="E28">
-        <v>-27.09084610091024</v>
+        <v>-29.02577700338164</v>
       </c>
       <c r="F28">
-        <v>-1.310348981528892</v>
+        <v>-2.348737342164573</v>
       </c>
       <c r="G28">
-        <v>-4.991121959131764</v>
+        <v>-6.002242019918127</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.40189796684739</v>
       </c>
       <c r="E29">
-        <v>-28.76863213533009</v>
+        <v>-27.9003017728333</v>
       </c>
       <c r="F29">
-        <v>-1.861056742951434</v>
+        <v>-1.877618292435604</v>
       </c>
       <c r="G29">
-        <v>-5.503720209341436</v>
+        <v>-5.943337483137875</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.778683557309378</v>
       </c>
       <c r="E30">
-        <v>-27.23053593862485</v>
+        <v>-28.99586190408697</v>
       </c>
       <c r="F30">
-        <v>-1.278945573288762</v>
+        <v>-1.906684047865033</v>
       </c>
       <c r="G30">
-        <v>-4.377320331786572</v>
+        <v>-6.073491581014322</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.12921342140169</v>
       </c>
       <c r="E31">
-        <v>-27.42540070364891</v>
+        <v>-29.51194718013412</v>
       </c>
       <c r="F31">
-        <v>-1.663157285320424</v>
+        <v>-1.746490217674651</v>
       </c>
       <c r="G31">
-        <v>-4.800133276425671</v>
+        <v>-6.48903456764918</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.45496318983371</v>
       </c>
       <c r="E32">
-        <v>-27.01530662598829</v>
+        <v>-28.88789402679609</v>
       </c>
       <c r="F32">
-        <v>-1.449743334602381</v>
+        <v>-1.978241737588466</v>
       </c>
       <c r="G32">
-        <v>-5.026021730206761</v>
+        <v>-5.990737874169159</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.75108311555977</v>
       </c>
       <c r="E33">
-        <v>-28.13135810212667</v>
+        <v>-28.66700412164995</v>
       </c>
       <c r="F33">
-        <v>-1.475358111431748</v>
+        <v>-1.882634885426958</v>
       </c>
       <c r="G33">
-        <v>-4.032103264042451</v>
+        <v>-5.538331962954516</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.02690110802611</v>
       </c>
       <c r="E34">
-        <v>-25.90295491311419</v>
+        <v>-27.96787113350175</v>
       </c>
       <c r="F34">
-        <v>-1.34375538214899</v>
+        <v>-1.774353183635215</v>
       </c>
       <c r="G34">
-        <v>-4.709278664645912</v>
+        <v>-5.517972107887998</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.29126508828338</v>
       </c>
       <c r="E35">
-        <v>-27.06913206804346</v>
+        <v>-27.77934170361442</v>
       </c>
       <c r="F35">
-        <v>-1.269260301615231</v>
+        <v>-1.990564531072511</v>
       </c>
       <c r="G35">
-        <v>-5.881079363726341</v>
+        <v>-6.449351058269936</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.5458688828015</v>
       </c>
       <c r="E36">
-        <v>-25.84291187624648</v>
+        <v>-27.84111008907905</v>
       </c>
       <c r="F36">
-        <v>-1.606149040659762</v>
+        <v>-2.04497087372098</v>
       </c>
       <c r="G36">
-        <v>-5.385533733589455</v>
+        <v>-5.820377200718265</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.79845805130582</v>
       </c>
       <c r="E37">
-        <v>-26.27577964969168</v>
+        <v>-27.41575052553857</v>
       </c>
       <c r="F37">
-        <v>-1.72693412002936</v>
+        <v>-1.998776965503866</v>
       </c>
       <c r="G37">
-        <v>-5.787281676962171</v>
+        <v>-5.746277259912757</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.04804912689399</v>
       </c>
       <c r="E38">
-        <v>-24.74520977678719</v>
+        <v>-27.01670139598265</v>
       </c>
       <c r="F38">
-        <v>-1.08914423538752</v>
+        <v>-1.894325634582668</v>
       </c>
       <c r="G38">
-        <v>-5.102621132894417</v>
+        <v>-6.022141709154686</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.29158748730546</v>
       </c>
       <c r="E39">
-        <v>-25.07440266630078</v>
+        <v>-26.31251915931591</v>
       </c>
       <c r="F39">
-        <v>-1.11734931708544</v>
+        <v>-2.066126548821077</v>
       </c>
       <c r="G39">
-        <v>-4.873114252838904</v>
+        <v>-5.610581308803571</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.5285806287327</v>
       </c>
       <c r="E40">
-        <v>-24.5202170741901</v>
+        <v>-25.92457837650081</v>
       </c>
       <c r="F40">
-        <v>-1.549137482529488</v>
+        <v>-1.670075809868605</v>
       </c>
       <c r="G40">
-        <v>-4.385378199629158</v>
+        <v>-5.834029890522219</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.74580983735389</v>
       </c>
       <c r="E41">
-        <v>-23.39480977075187</v>
+        <v>-25.98401006937748</v>
       </c>
       <c r="F41">
-        <v>-1.663800926792399</v>
+        <v>-1.892816349174767</v>
       </c>
       <c r="G41">
-        <v>-4.506842115465018</v>
+        <v>-5.707325381097693</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.93812790125415</v>
       </c>
       <c r="E42">
-        <v>-23.85435931305026</v>
+        <v>-25.71134159242763</v>
       </c>
       <c r="F42">
-        <v>-1.343701538267808</v>
+        <v>-2.035460387569439</v>
       </c>
       <c r="G42">
-        <v>-5.202324832900648</v>
+        <v>-6.127632242763562</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.10234603804403</v>
       </c>
       <c r="E43">
-        <v>-23.3560369762982</v>
+        <v>-26.99958829270767</v>
       </c>
       <c r="F43">
-        <v>-1.455511256828074</v>
+        <v>-1.521305166162828</v>
       </c>
       <c r="G43">
-        <v>-4.286032038541169</v>
+        <v>-5.360896653686199</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.22809429644647</v>
       </c>
       <c r="E44">
-        <v>-23.27320212974989</v>
+        <v>-23.36879821605181</v>
       </c>
       <c r="F44">
-        <v>-1.676154369870348</v>
+        <v>-2.086519297543195</v>
       </c>
       <c r="G44">
-        <v>-5.191880061724247</v>
+        <v>-5.917568196660188</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.31385556262501</v>
       </c>
       <c r="E45">
-        <v>-21.78231980304863</v>
+        <v>-24.04871236051146</v>
       </c>
       <c r="F45">
-        <v>-1.178087700160909</v>
+        <v>-1.885858891358654</v>
       </c>
       <c r="G45">
-        <v>-5.323517284002287</v>
+        <v>-5.470104929935677</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.35781597376944</v>
       </c>
       <c r="E46">
-        <v>-21.9836240581116</v>
+        <v>-23.46714308607639</v>
       </c>
       <c r="F46">
-        <v>-1.272312835494547</v>
+        <v>-1.490338307543974</v>
       </c>
       <c r="G46">
-        <v>-5.600288822721977</v>
+        <v>-5.066172026507042</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.35875752939564</v>
       </c>
       <c r="E47">
-        <v>-21.86746869981485</v>
+        <v>-22.86344768763985</v>
       </c>
       <c r="F47">
-        <v>-1.318510885548675</v>
+        <v>-1.260512741841668</v>
       </c>
       <c r="G47">
-        <v>-5.144873625612136</v>
+        <v>-5.630686251863565</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.32396344052266</v>
       </c>
       <c r="E48">
-        <v>-20.32029291272424</v>
+        <v>-22.67982712357683</v>
       </c>
       <c r="F48">
-        <v>-1.057304277526115</v>
+        <v>-1.880337822618995</v>
       </c>
       <c r="G48">
-        <v>-4.21157786936296</v>
+        <v>-5.931310271193703</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.2527993548719</v>
       </c>
       <c r="E49">
-        <v>-19.52481211158885</v>
+        <v>-23.0758421755476</v>
       </c>
       <c r="F49">
-        <v>-1.293350054056043</v>
+        <v>-1.880103394644003</v>
       </c>
       <c r="G49">
-        <v>-5.45114874617781</v>
+        <v>-5.578280315976902</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.14990174802399</v>
       </c>
       <c r="E50">
-        <v>-19.54112820343848</v>
+        <v>-21.49529153502046</v>
       </c>
       <c r="F50">
-        <v>-1.786188897086415</v>
+        <v>-1.714070402631287</v>
       </c>
       <c r="G50">
-        <v>-5.640422566294562</v>
+        <v>-6.029454704250936</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.02589381534477</v>
       </c>
       <c r="E51">
-        <v>-19.07533389548352</v>
+        <v>-21.15203773371305</v>
       </c>
       <c r="F51">
-        <v>-1.280167415207892</v>
+        <v>-1.864660141153612</v>
       </c>
       <c r="G51">
-        <v>-4.617702353938592</v>
+        <v>-5.677196106144786</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.88164839607213</v>
       </c>
       <c r="E52">
-        <v>-18.36135204106417</v>
+        <v>-20.78131873754912</v>
       </c>
       <c r="F52">
-        <v>-1.406668229656807</v>
+        <v>-1.837020006024401</v>
       </c>
       <c r="G52">
-        <v>-6.433864326237226</v>
+        <v>-6.348528393871432</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.72409616398905</v>
       </c>
       <c r="E53">
-        <v>-19.07278889309121</v>
+        <v>-19.7944148116355</v>
       </c>
       <c r="F53">
-        <v>-1.505704522865905</v>
+        <v>-1.532564335901679</v>
       </c>
       <c r="G53">
-        <v>-5.492732508696595</v>
+        <v>-6.708639605996734</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.56043485693736</v>
       </c>
       <c r="E54">
-        <v>-18.85892717960497</v>
+        <v>-20.36958535229773</v>
       </c>
       <c r="F54">
-        <v>-1.609194947599855</v>
+        <v>-1.638305434869036</v>
       </c>
       <c r="G54">
-        <v>-6.272445436287902</v>
+        <v>-7.263910788207612</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.3935916758568</v>
       </c>
       <c r="E55">
-        <v>-18.37645903035376</v>
+        <v>-19.66161731136057</v>
       </c>
       <c r="F55">
-        <v>-0.9105565070179747</v>
+        <v>-1.8260714740616</v>
       </c>
       <c r="G55">
-        <v>-6.63584733067924</v>
+        <v>-6.723033858001486</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.2332570085982</v>
       </c>
       <c r="E56">
-        <v>-16.50685589391701</v>
+        <v>-19.48004814602303</v>
       </c>
       <c r="F56">
-        <v>-1.789958797136555</v>
+        <v>-1.60292337799326</v>
       </c>
       <c r="G56">
-        <v>-4.711678810161883</v>
+        <v>-6.500545334489226</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.07948573361263</v>
       </c>
       <c r="E57">
-        <v>-15.55020670284864</v>
+        <v>-18.58535753632759</v>
       </c>
       <c r="F57">
-        <v>-1.436414903091337</v>
+        <v>-1.74141232549549</v>
       </c>
       <c r="G57">
-        <v>-5.857405652575013</v>
+        <v>-7.187890730989328</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.93358809838179</v>
       </c>
       <c r="E58">
-        <v>-16.85371436053452</v>
+        <v>-18.24170522930751</v>
       </c>
       <c r="F58">
-        <v>-0.7016960919131213</v>
+        <v>-1.642637796385677</v>
       </c>
       <c r="G58">
-        <v>-5.95575865000122</v>
+        <v>-7.294513471172635</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.80323817798252</v>
       </c>
       <c r="E59">
-        <v>-16.65847826064183</v>
+        <v>-18.1794704110201</v>
       </c>
       <c r="F59">
-        <v>-1.557432753701123</v>
+        <v>-1.388594081295125</v>
       </c>
       <c r="G59">
-        <v>-5.902948827558767</v>
+        <v>-7.030173030952909</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.68345882863338</v>
       </c>
       <c r="E60">
-        <v>-14.26997087308816</v>
+        <v>-17.95529283374438</v>
       </c>
       <c r="F60">
-        <v>-1.279441765363039</v>
+        <v>-1.684353550423257</v>
       </c>
       <c r="G60">
-        <v>-6.006760914579233</v>
+        <v>-6.908652835842882</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.57357617376967</v>
       </c>
       <c r="E61">
-        <v>-15.15290556425968</v>
+        <v>-17.33221103808101</v>
       </c>
       <c r="F61">
-        <v>-0.829620869927449</v>
+        <v>-1.793382439612325</v>
       </c>
       <c r="G61">
-        <v>-6.523507278349611</v>
+        <v>-7.332588055419793</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.47197353978438</v>
       </c>
       <c r="E62">
-        <v>-14.09832359430143</v>
+        <v>-16.65634082091021</v>
       </c>
       <c r="F62">
-        <v>-0.9999663426391393</v>
+        <v>-1.971348064062368</v>
       </c>
       <c r="G62">
-        <v>-6.824541805326619</v>
+        <v>-7.062530303053746</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.37222678005351</v>
       </c>
       <c r="E63">
-        <v>-14.581597811926</v>
+        <v>-18.00876052635295</v>
       </c>
       <c r="F63">
-        <v>-1.727409602918567</v>
+        <v>-1.773500793577734</v>
       </c>
       <c r="G63">
-        <v>-6.91365838069826</v>
+        <v>-7.849112612639041</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.27446731119396</v>
       </c>
       <c r="E64">
-        <v>-15.17479620761276</v>
+        <v>-16.33759059245831</v>
       </c>
       <c r="F64">
-        <v>-1.65218141723333</v>
+        <v>-1.861892565660858</v>
       </c>
       <c r="G64">
-        <v>-6.770768614132237</v>
+        <v>-7.176330305966193</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.17022738884706</v>
       </c>
       <c r="E65">
-        <v>-14.79994271467983</v>
+        <v>-16.46733590125207</v>
       </c>
       <c r="F65">
-        <v>-1.195350048467848</v>
+        <v>-2.120712647195953</v>
       </c>
       <c r="G65">
-        <v>-5.785907800563373</v>
+        <v>-8.124801602967388</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.05185369673548</v>
       </c>
       <c r="E66">
-        <v>-14.01647595508679</v>
+        <v>-16.24717508042117</v>
       </c>
       <c r="F66">
-        <v>-1.530673173121087</v>
+        <v>-1.69641209470581</v>
       </c>
       <c r="G66">
-        <v>-7.004099174285609</v>
+        <v>-7.246229164482365</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.92042858901546</v>
       </c>
       <c r="E67">
-        <v>-14.40514129374312</v>
+        <v>-16.52086246402274</v>
       </c>
       <c r="F67">
-        <v>-1.462813315483752</v>
+        <v>-2.12436906091191</v>
       </c>
       <c r="G67">
-        <v>-6.216334999942795</v>
+        <v>-8.4181821486576</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.7678349711465</v>
       </c>
       <c r="E68">
-        <v>-14.89461046381018</v>
+        <v>-16.11797318850832</v>
       </c>
       <c r="F68">
-        <v>-2.08447323005828</v>
+        <v>-1.97980238177534</v>
       </c>
       <c r="G68">
-        <v>-6.843643653088214</v>
+        <v>-7.814851776853123</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.59276937866231</v>
       </c>
       <c r="E69">
-        <v>-14.90091409962886</v>
+        <v>-15.67632923243626</v>
       </c>
       <c r="F69">
-        <v>-1.455861656239458</v>
+        <v>-2.044501189403593</v>
       </c>
       <c r="G69">
-        <v>-5.731555263899619</v>
+        <v>-7.726708501870028</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.39601723699985</v>
       </c>
       <c r="E70">
-        <v>-13.8547732052209</v>
+        <v>-14.86924195241921</v>
       </c>
       <c r="F70">
-        <v>-1.791934453392232</v>
+        <v>-1.656051549739209</v>
       </c>
       <c r="G70">
-        <v>-6.634251647729311</v>
+        <v>-8.348405780326383</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.17666176825253</v>
       </c>
       <c r="E71">
-        <v>-13.37961854149208</v>
+        <v>-16.69020927801358</v>
       </c>
       <c r="F71">
-        <v>-1.093010226056385</v>
+        <v>-2.281120196176257</v>
       </c>
       <c r="G71">
-        <v>-6.652823808204622</v>
+        <v>-7.908550147251115</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.94281318374267</v>
       </c>
       <c r="E72">
-        <v>-12.01781583790545</v>
+        <v>-16.09720107823514</v>
       </c>
       <c r="F72">
-        <v>-1.47255077430366</v>
+        <v>-1.644432040180141</v>
       </c>
       <c r="G72">
-        <v>-6.850797741998578</v>
+        <v>-8.472855808238664</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.697222282021158</v>
       </c>
       <c r="E73">
-        <v>-14.31990182749674</v>
+        <v>-17.18839576054541</v>
       </c>
       <c r="F73">
-        <v>-1.60813712242648</v>
+        <v>-1.887546275758156</v>
       </c>
       <c r="G73">
-        <v>-6.142784609696807</v>
+        <v>-7.466797571581847</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.444059566510312</v>
       </c>
       <c r="E74">
-        <v>-15.2169744145202</v>
+        <v>-15.51212676491813</v>
       </c>
       <c r="F74">
-        <v>-1.976738250752385</v>
+        <v>-2.245901327678834</v>
       </c>
       <c r="G74">
-        <v>-6.536454821953701</v>
+        <v>-7.607048833353071</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.196605314607778</v>
       </c>
       <c r="E75">
-        <v>-16.59843069530012</v>
+        <v>-15.78245402080602</v>
       </c>
       <c r="F75">
-        <v>-1.414576653251334</v>
+        <v>-2.175093310454935</v>
       </c>
       <c r="G75">
-        <v>-6.634976657202412</v>
+        <v>-7.507897994451898</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.958588210569703</v>
       </c>
       <c r="E76">
-        <v>-14.96119714561897</v>
+        <v>-16.93550765806107</v>
       </c>
       <c r="F76">
-        <v>-1.682789592766772</v>
+        <v>-2.45736364479588</v>
       </c>
       <c r="G76">
-        <v>-6.794899180567985</v>
+        <v>-7.691275732963208</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.739337772882285</v>
       </c>
       <c r="E77">
-        <v>-14.37906181193294</v>
+        <v>-17.39972605706136</v>
       </c>
       <c r="F77">
-        <v>-2.092443781208017</v>
+        <v>-2.557770057689209</v>
       </c>
       <c r="G77">
-        <v>-5.04918892789058</v>
+        <v>-7.19833219162019</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.545506420934437</v>
       </c>
       <c r="E78">
-        <v>-15.64824363664069</v>
+        <v>-17.55303754459104</v>
       </c>
       <c r="F78">
-        <v>-2.624567119948752</v>
+        <v>-2.659128264728353</v>
       </c>
       <c r="G78">
-        <v>-6.778611296514771</v>
+        <v>-7.433526588912171</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.379433220541888</v>
       </c>
       <c r="E79">
-        <v>-15.48444873178325</v>
+        <v>-16.92734281942524</v>
       </c>
       <c r="F79">
-        <v>-1.798893567943151</v>
+        <v>-2.437935115730621</v>
       </c>
       <c r="G79">
-        <v>-5.769735785604033</v>
+        <v>-7.435949908246918</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.246685344359703</v>
       </c>
       <c r="E80">
-        <v>-15.50436043199498</v>
+        <v>-17.53770413160107</v>
       </c>
       <c r="F80">
-        <v>-2.297804344036043</v>
+        <v>-2.625537966544833</v>
       </c>
       <c r="G80">
-        <v>-6.169801971842799</v>
+        <v>-6.779101257254583</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.143504532807338</v>
       </c>
       <c r="E81">
-        <v>-15.82999394093854</v>
+        <v>-18.74407149334842</v>
       </c>
       <c r="F81">
-        <v>-2.497898975284472</v>
+        <v>-2.659269915554232</v>
       </c>
       <c r="G81">
-        <v>-6.415758952682951</v>
+        <v>-6.578402744481806</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.066220566248765</v>
       </c>
       <c r="E82">
-        <v>-17.16863349997594</v>
+        <v>-19.11020767381659</v>
       </c>
       <c r="F82">
-        <v>-2.465040953885026</v>
+        <v>-2.798736336591765</v>
       </c>
       <c r="G82">
-        <v>-6.17556894217221</v>
+        <v>-7.760035763813871</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.016842875523441</v>
       </c>
       <c r="E83">
-        <v>-18.03374864592728</v>
+        <v>-20.11640289900289</v>
       </c>
       <c r="F83">
-        <v>-2.892626811494672</v>
+        <v>-2.942264243005224</v>
       </c>
       <c r="G83">
-        <v>-5.053370146906681</v>
+        <v>-6.376280697127143</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.988498043825658</v>
       </c>
       <c r="E84">
-        <v>-18.7216238476924</v>
+        <v>-20.83583703612747</v>
       </c>
       <c r="F84">
-        <v>-2.277305564286366</v>
+        <v>-2.86937453849809</v>
       </c>
       <c r="G84">
-        <v>-5.681003233514947</v>
+        <v>-6.938444435150783</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.981022607190537</v>
       </c>
       <c r="E85">
-        <v>-20.3010242558216</v>
+        <v>-20.92259354116642</v>
       </c>
       <c r="F85">
-        <v>-1.905195471642203</v>
+        <v>-2.905458222564036</v>
       </c>
       <c r="G85">
-        <v>-4.628554322216323</v>
+        <v>-7.020238083789557</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.990045717548794</v>
       </c>
       <c r="E86">
-        <v>-21.26744136532452</v>
+        <v>-22.44412005147759</v>
       </c>
       <c r="F86">
-        <v>-2.739843556089734</v>
+        <v>-3.330611165111661</v>
       </c>
       <c r="G86">
-        <v>-6.223267282302029</v>
+        <v>-6.949365924884839</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.015539518082157</v>
       </c>
       <c r="E87">
-        <v>-20.95636690031562</v>
+        <v>-23.37151982893042</v>
       </c>
       <c r="F87">
-        <v>-2.877032795136972</v>
+        <v>-3.16174515658137</v>
       </c>
       <c r="G87">
-        <v>-6.324569975803727</v>
+        <v>-6.770245547937032</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.0626214352038</v>
       </c>
       <c r="E88">
-        <v>-22.45999235287447</v>
+        <v>-22.87808824410665</v>
       </c>
       <c r="F88">
-        <v>-2.588546391805418</v>
+        <v>-3.725711766653121</v>
       </c>
       <c r="G88">
-        <v>-4.47562367102969</v>
+        <v>-6.802486950943994</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.130609301480694</v>
       </c>
       <c r="E89">
-        <v>-23.87178035255777</v>
+        <v>-25.60036680839566</v>
       </c>
       <c r="F89">
-        <v>-3.039216363828878</v>
+        <v>-3.521141466327366</v>
       </c>
       <c r="G89">
-        <v>-4.952434923959841</v>
+        <v>-7.077037113606832</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.22512774261307</v>
       </c>
       <c r="E90">
-        <v>-25.1289662496192</v>
+        <v>-26.45396604494549</v>
       </c>
       <c r="F90">
-        <v>-3.114847964439279</v>
+        <v>-3.492708583593676</v>
       </c>
       <c r="G90">
-        <v>-7.262076745978856</v>
+        <v>-7.020373816156667</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.353728508312473</v>
       </c>
       <c r="E91">
-        <v>-28.7257791857955</v>
+        <v>-27.24666636304017</v>
       </c>
       <c r="F91">
-        <v>-3.470341006983284</v>
+        <v>-3.342857748794648</v>
       </c>
       <c r="G91">
-        <v>-6.698840391200492</v>
+        <v>-7.202609416456927</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.517698701373551</v>
       </c>
       <c r="E92">
-        <v>-28.49853130314259</v>
+        <v>-29.0396250768971</v>
       </c>
       <c r="F92">
-        <v>-3.767912943988742</v>
+        <v>-3.858047601087356</v>
       </c>
       <c r="G92">
-        <v>-7.593157784270288</v>
+        <v>-7.904051115863246</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.723411034390008</v>
       </c>
       <c r="E93">
-        <v>-30.28304894144922</v>
+        <v>-31.35295526744943</v>
       </c>
       <c r="F93">
-        <v>-3.197176087133911</v>
+        <v>-3.531694038671629</v>
       </c>
       <c r="G93">
-        <v>-6.6831782002542</v>
+        <v>-7.902515022733025</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.96456115741033</v>
       </c>
       <c r="E94">
-        <v>-32.17943120893032</v>
+        <v>-32.3119592650018</v>
       </c>
       <c r="F94">
-        <v>-3.371825756870547</v>
+        <v>-3.789766932809398</v>
       </c>
       <c r="G94">
-        <v>-6.629643368338646</v>
+        <v>-7.805542522796692</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.238728359432006</v>
       </c>
       <c r="E95">
-        <v>-33.52944403043798</v>
+        <v>-34.12837547421845</v>
       </c>
       <c r="F95">
-        <v>-2.940503962274275</v>
+        <v>-4.018403791288687</v>
       </c>
       <c r="G95">
-        <v>-6.837058978010603</v>
+        <v>-7.219311118702551</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.541894545286468</v>
       </c>
       <c r="E96">
-        <v>-34.9343419569186</v>
+        <v>-36.5828129148498</v>
       </c>
       <c r="F96">
-        <v>-3.718371603096915</v>
+        <v>-4.015207121481284</v>
       </c>
       <c r="G96">
-        <v>-6.589628804405475</v>
+        <v>-8.469022196504188</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.855792511080292</v>
       </c>
       <c r="E97">
-        <v>-35.70274474772513</v>
+        <v>-37.70046747078688</v>
       </c>
       <c r="F97">
-        <v>-3.543560401716732</v>
+        <v>-3.911633860007053</v>
       </c>
       <c r="G97">
-        <v>-7.414126792052042</v>
+        <v>-8.205247859571678</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.17143107648919</v>
       </c>
       <c r="E98">
-        <v>-39.42833842773156</v>
+        <v>-39.88376479444597</v>
       </c>
       <c r="F98">
-        <v>-3.854726676169533</v>
+        <v>-3.788804369887345</v>
       </c>
       <c r="G98">
-        <v>-6.542698510840767</v>
+        <v>-8.36094943737468</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.46894423675542</v>
       </c>
       <c r="E99">
-        <v>-41.79046745419055</v>
+        <v>-41.98005654699568</v>
       </c>
       <c r="F99">
-        <v>-3.899500762658249</v>
+        <v>-4.038955586552142</v>
       </c>
       <c r="G99">
-        <v>-8.054412783711404</v>
+        <v>-9.188102482543744</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.73962576896333</v>
       </c>
       <c r="E100">
-        <v>-43.58035359843327</v>
+        <v>-44.09874839622433</v>
       </c>
       <c r="F100">
-        <v>-3.659438232592147</v>
+        <v>-4.244539808578924</v>
       </c>
       <c r="G100">
-        <v>-7.446639659793225</v>
+        <v>-8.580600823359784</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.9586165744365</v>
       </c>
       <c r="E101">
-        <v>-46.092875510924</v>
+        <v>-45.49741740670741</v>
       </c>
       <c r="F101">
-        <v>-3.675137451610003</v>
+        <v>-3.902274136722822</v>
       </c>
       <c r="G101">
-        <v>-6.687862622192268</v>
+        <v>-9.528410011253126</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.1368943815389</v>
       </c>
       <c r="E102">
-        <v>-47.43332193109045</v>
+        <v>-47.94457985384543</v>
       </c>
       <c r="F102">
-        <v>-3.7494660302958</v>
+        <v>-4.273312321947762</v>
       </c>
       <c r="G102">
-        <v>-7.438108383938522</v>
+        <v>-8.154705760823624</v>
       </c>
     </row>
   </sheetData>
